--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,130 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122619436</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57263</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kärrstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>629359</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6533057</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sättersta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mauri Karlsberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mauri Karlsberg, Christopher  Karlsberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122619436</v>
       </c>
       <c r="B3" t="n">
-        <v>57263</v>
+        <v>57264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122619436</v>
       </c>
       <c r="B3" t="n">
-        <v>57264</v>
+        <v>57358</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -802,12 +802,7 @@
         <v>122619436</v>
       </c>
       <c r="B3" t="n">
-        <v>57358</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57763</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122619436</v>
       </c>
       <c r="B3" t="n">
-        <v>57763</v>
+        <v>57765</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122619436</v>
       </c>
       <c r="B3" t="n">
-        <v>57765</v>
+        <v>57773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122619436</v>
       </c>
       <c r="B3" t="n">
-        <v>57773</v>
+        <v>57774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122619436</v>
       </c>
       <c r="B3" t="n">
-        <v>57774</v>
+        <v>57775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83854981</v>
+        <v>122619436</v>
       </c>
       <c r="B2" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102999</v>
+        <v>100011</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629358.8132359438</v>
+        <v>629359</v>
       </c>
       <c r="R2" t="n">
-        <v>6533056.676418257</v>
+        <v>6533057</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Sjöstedt</t>
+          <t>Mauri Karlsberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Sjöstedt, ingvar jansson</t>
+          <t>Mauri Karlsberg, Christopher  Karlsberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122619436</v>
+        <v>83854981</v>
       </c>
       <c r="B3" t="n">
-        <v>57795</v>
+        <v>58393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,33 +805,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100011</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -876,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2020-03-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2020-03-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mauri Karlsberg</t>
+          <t>Jan Sjöstedt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mauri Karlsberg, Christopher  Karlsberg</t>
+          <t>Jan Sjöstedt, ingvar jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 56420-2021 artfynd.xlsx
+++ b/artfynd/A 56420-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122619436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,8 +920,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83854981</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>